--- a/salidas/empresas/CRWD.xlsx
+++ b/salidas/empresas/CRWD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B3" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B4" t="n">
@@ -551,7 +563,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B5" t="n">
@@ -576,7 +588,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B6" t="n">
@@ -601,7 +613,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B7" t="n">
@@ -626,7 +638,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B8" t="n">
@@ -651,7 +663,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B9" t="n">
@@ -676,7 +688,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B10" t="n">
@@ -701,7 +713,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B11" t="n">
@@ -728,7 +740,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B12" t="n">
@@ -755,7 +767,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B13" t="n">
@@ -782,7 +794,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B14" t="n">
@@ -809,7 +821,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B15" t="n">
@@ -836,7 +848,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B16" t="n">
@@ -863,7 +875,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B17" t="n">
@@ -890,7 +902,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B18" t="n">
@@ -915,7 +927,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B19" t="n">
@@ -940,7 +952,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B20" t="n">
@@ -965,7 +977,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B21" t="n">
@@ -990,7 +1002,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B22" t="n">
@@ -1015,7 +1027,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B23" t="n">
@@ -1040,7 +1052,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B24" t="n">
@@ -1065,7 +1077,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B25" t="n">
@@ -1090,7 +1102,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B26" t="n">
@@ -1117,7 +1129,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B27" t="n">
@@ -1144,7 +1156,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B28" t="n">
@@ -1171,7 +1183,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B29" t="n">
@@ -1198,7 +1210,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B30" t="n">
@@ -1225,7 +1237,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B31" t="n">
@@ -1252,7 +1264,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B32" t="n">
@@ -1279,7 +1291,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B33" t="n">
@@ -1306,7 +1318,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B34" t="n">
@@ -1333,7 +1345,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B35" t="n">
@@ -1360,7 +1372,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B36" t="n">
@@ -1387,7 +1399,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B37" t="n">
@@ -1414,7 +1426,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B38" t="n">
@@ -1441,7 +1453,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B39" t="n">
@@ -1468,7 +1480,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B40" t="n">
@@ -1495,7 +1507,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B41" t="n">
@@ -1522,7 +1534,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B42" t="n">
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B43" t="n">
@@ -1576,7 +1588,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B44" t="n">
@@ -1603,7 +1615,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B45" t="n">
@@ -1630,7 +1642,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B46" t="n">
@@ -1657,7 +1669,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B47" t="n">
@@ -1684,7 +1696,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B48" t="n">
@@ -1711,7 +1723,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B49" t="n">
@@ -1738,7 +1750,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B50" t="n">
@@ -1765,7 +1777,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B51" t="n">
@@ -1792,7 +1804,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B52" t="n">
@@ -1819,7 +1831,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B53" t="n">
@@ -1846,7 +1858,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B54" t="n">
@@ -1873,7 +1885,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B55" t="n">
@@ -1900,7 +1912,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B56" t="n">
@@ -1927,7 +1939,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B57" t="n">
@@ -1954,7 +1966,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B58" t="n">
@@ -1981,7 +1993,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B59" t="n">
@@ -2010,7 +2022,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B60" t="n">
@@ -2039,7 +2051,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B61" t="n">
@@ -2068,7 +2080,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B62" t="n">
@@ -2097,7 +2109,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B63" t="n">
@@ -2126,7 +2138,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B64" t="n">
@@ -2155,7 +2167,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B65" t="n">
@@ -2184,7 +2196,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B66" t="n">
@@ -2213,7 +2225,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B67" t="n">
@@ -2242,7 +2254,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B68" t="n">
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B69" t="n">
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B70" t="n">
@@ -2329,7 +2341,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B71" t="n">
@@ -2356,7 +2368,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B72" t="n">
@@ -2383,7 +2395,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B73" t="n">
@@ -2410,7 +2422,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B74" t="n">
@@ -2437,7 +2449,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B75" t="n">
@@ -2464,7 +2476,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B76" t="n">
@@ -2491,7 +2503,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B77" t="n">
@@ -2518,7 +2530,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B78" t="n">
@@ -2545,7 +2557,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B79" t="n">
@@ -2572,7 +2584,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B80" t="n">
@@ -2599,7 +2611,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B81" t="n">
@@ -2626,7 +2638,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B82" t="n">
@@ -2653,7 +2665,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B83" t="n">
@@ -2680,7 +2692,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B84" t="n">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B85" t="n">
@@ -2734,7 +2746,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B86" t="n">
@@ -2761,7 +2773,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B87" t="n">
@@ -2788,7 +2800,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B88" t="n">
@@ -2817,32 +2829,32 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B89" t="n">
-        <v>262.489990234375</v>
+        <v>259.6700134277344</v>
       </c>
       <c r="C89" t="n">
-        <v>262.489990234375</v>
+        <v>259.6700134277344</v>
       </c>
       <c r="D89" t="n">
-        <v>196236200</v>
+        <v>204644000</v>
       </c>
       <c r="E89" t="n">
         <v>0.06249999999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>4199.839843750001</v>
+        <v>4154.720214843751</v>
       </c>
       <c r="G89" t="n">
         <v>1023934842</v>
       </c>
       <c r="H89" t="n">
-        <v>268772646677.2163</v>
+        <v>265885174171.2651</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1916491088599952</v>
+        <v>0.1998603735373232</v>
       </c>
     </row>
   </sheetData>
@@ -2874,75 +2886,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -2978,13 +2990,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>43714</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -3020,13 +3032,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>43805</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -3062,13 +3074,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -3095,7 +3107,7 @@
       <c r="I5" t="n">
         <v>-0.78</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="K5" t="n">
@@ -3108,13 +3120,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -3141,7 +3153,7 @@
       <c r="I6" t="n">
         <v>-0.725</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="K6" t="n">
@@ -3154,13 +3166,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>43714</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -3187,7 +3199,7 @@
       <c r="I7" t="n">
         <v>-0.6375</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="K7" t="n">
@@ -3200,13 +3212,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>43805</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -3233,7 +3245,7 @@
       <c r="I8" t="n">
         <v>-0.4475</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="K8" t="n">
@@ -3246,13 +3258,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -3279,7 +3291,7 @@
       <c r="I9" t="n">
         <v>-0.24</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="K9" t="n">
@@ -3292,13 +3304,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -3325,7 +3337,7 @@
       <c r="I10" t="n">
         <v>-0.125</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="K10" t="n">
@@ -3338,13 +3350,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -3371,7 +3383,7 @@
       <c r="I11" t="n">
         <v>-0.05999999999999997</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="K11" t="n">
@@ -3384,13 +3396,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -3417,7 +3429,7 @@
       <c r="I12" t="n">
         <v>-0.04499999999999997</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="K12" t="n">
@@ -3430,13 +3442,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -3463,7 +3475,7 @@
       <c r="I13" t="n">
         <v>-0.1075</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="K13" t="n">
@@ -3476,13 +3488,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -3509,7 +3521,7 @@
       <c r="I14" t="n">
         <v>-0.18</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="K14" t="n">
@@ -3522,13 +3534,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -3555,7 +3567,7 @@
       <c r="I15" t="n">
         <v>-0.2075</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="K15" t="n">
@@ -3568,13 +3580,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -3601,7 +3613,7 @@
       <c r="I16" t="n">
         <v>-0.235</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="K16" t="n">
@@ -3614,13 +3626,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -3647,7 +3659,7 @@
       <c r="I17" t="n">
         <v>-0.2575</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="K17" t="n">
@@ -3660,13 +3672,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -3693,7 +3705,7 @@
       <c r="I18" t="n">
         <v>-0.1975</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="K18" t="n">
@@ -3706,13 +3718,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -3739,7 +3751,7 @@
       <c r="I19" t="n">
         <v>-0.1875</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="K19" t="n">
@@ -3752,13 +3764,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -3785,7 +3797,7 @@
       <c r="I20" t="n">
         <v>-0.1925</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="K20" t="n">
@@ -3798,13 +3810,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -3831,7 +3843,7 @@
       <c r="I21" t="n">
         <v>-0.1975</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="K21" t="n">
@@ -3844,13 +3856,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -3877,7 +3889,7 @@
       <c r="I22" t="n">
         <v>-0.1625</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="K22" t="n">
@@ -3890,13 +3902,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -3923,7 +3935,7 @@
       <c r="I23" t="n">
         <v>-0.1025</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="K23" t="n">
@@ -3936,13 +3948,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45139</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -3969,7 +3981,7 @@
       <c r="I24" t="n">
         <v>-0.01500000000000002</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="K24" t="n">
@@ -3982,13 +3994,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45231</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>45358</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -4015,7 +4027,7 @@
       <c r="I25" t="n">
         <v>0.0925</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>45358</v>
       </c>
       <c r="K25" t="n">
@@ -4028,13 +4040,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>45448</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -4061,7 +4073,7 @@
       <c r="I26" t="n">
         <v>0.135</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>45448</v>
       </c>
       <c r="K26" t="n">
@@ -4074,13 +4086,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -4107,7 +4119,7 @@
       <c r="I27" t="n">
         <v>0.175</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="K27" t="n">
@@ -4120,13 +4132,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -4153,7 +4165,7 @@
       <c r="I28" t="n">
         <v>0.13</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="K28" t="n">
@@ -4166,13 +4178,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -4199,7 +4211,7 @@
       <c r="I29" t="n">
         <v>-0.01999999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="K29" t="n">
@@ -4212,13 +4224,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>45812</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -4245,7 +4257,7 @@
       <c r="I30" t="n">
         <v>-0.1725</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>45812</v>
       </c>
       <c r="K30" t="n">
@@ -4258,13 +4270,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45778</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -4291,7 +4303,7 @@
       <c r="I31" t="n">
         <v>-0.2975</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="K31" t="n">
@@ -4304,13 +4316,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -4337,7 +4349,7 @@
       <c r="I32" t="n">
         <v>-0.3150000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="K32" t="n">
@@ -4350,13 +4362,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>46086</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -4383,7 +4395,7 @@
       <c r="I33" t="n">
         <v>-0.1625</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>46086</v>
       </c>
       <c r="K33" t="n">
@@ -4396,13 +4408,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>46177</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -4429,7 +4441,7 @@
       <c r="I34" t="n">
         <v>-0.025</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>46177</v>
       </c>
       <c r="K34" t="n">
@@ -4442,13 +4454,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -4475,7 +4487,7 @@
       <c r="I35" t="n">
         <v>0.06249999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="K35" t="n">
@@ -4513,57 +4525,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="C2" t="n">
@@ -4593,10 +4605,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="C3" t="n">
@@ -4626,10 +4638,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>43805</v>
       </c>
       <c r="C4" t="n">
@@ -4663,10 +4675,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="C5" t="n">
@@ -4700,10 +4712,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43913</v>
       </c>
       <c r="C6" t="n">
@@ -4737,10 +4749,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43985</v>
       </c>
       <c r="C7" t="n">
@@ -4774,10 +4786,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44077</v>
       </c>
       <c r="C8" t="n">
@@ -4811,10 +4823,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44168</v>
       </c>
       <c r="C9" t="n">
@@ -4848,10 +4860,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="C10" t="n">
@@ -4885,10 +4897,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="C11" t="n">
@@ -4922,10 +4934,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="C12" t="n">
@@ -4959,10 +4971,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="C13" t="n">
@@ -4996,10 +5008,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="C14" t="n">
@@ -5033,10 +5045,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="C15" t="n">
@@ -5070,10 +5082,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="C16" t="n">
@@ -5107,10 +5119,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="C17" t="n">
@@ -5144,10 +5156,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>44636</v>
       </c>
       <c r="C18" t="n">
@@ -5181,10 +5193,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="C19" t="n">
@@ -5218,10 +5230,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="C20" t="n">
@@ -5255,10 +5267,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="C21" t="n">
@@ -5292,10 +5304,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="C22" t="n">
@@ -5329,10 +5341,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="C23" t="n">
@@ -5366,10 +5378,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="C24" t="n">
@@ -5403,10 +5415,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>45259</v>
       </c>
       <c r="C25" t="n">
@@ -5440,10 +5452,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>45358</v>
       </c>
       <c r="C26" t="n">
@@ -5477,10 +5489,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45448</v>
       </c>
       <c r="C27" t="n">
@@ -5514,10 +5526,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="C28" t="n">
@@ -5551,10 +5563,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="C29" t="n">
@@ -5588,10 +5600,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45806</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45812</v>
       </c>
       <c r="C30" t="n">
@@ -5621,10 +5633,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45890</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="C31" t="n">
@@ -5654,10 +5666,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45986</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>45994</v>
       </c>
       <c r="C32" t="n">
@@ -5687,10 +5699,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46170</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>46177</v>
       </c>
       <c r="C33" t="n">
@@ -5720,10 +5732,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46254</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="C34" t="n">
@@ -5771,12 +5783,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
